--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIKRAM\Desktop\OPHC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/803ce9435f8f2a27/Desktop/OPHC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0821558B-90FF-490C-86E1-A2C1D1CA221C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{0821558B-90FF-490C-86E1-A2C1D1CA221C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1C6251-9732-4501-B5A7-23628257BC17}"/>
   <bookViews>
     <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>OPHC</t>
   </si>
@@ -145,310 +145,43 @@
     <t>Doctor is a dedicated General Physician with over 12 years of clinical experience in diagnosing and treating a wide range of acute and chronic medical conditions. He specializes in diabetes management, hypertension, preventive healthcare, and infectious diseases. Dr.Kumar is committed to providing patient-centered care through accurate diagnosis, evidence-based treatment, and personalized health guidance.</t>
   </si>
   <si>
-    <t>C:\TestData\MedicalReport_21072026_182510_985.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_22072026_123510_525.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_24072026_160050_513.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_24072026_160054_333.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_24072026_161505_035.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_24072026_161508_662.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_24072026_161906_534.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_24072026_161910_796.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_24072026_163042_764.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_24072026_163046_316.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_101337_253.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_101340_463.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_111710_588.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_111714_171.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_114915_921.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_114919_490.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_120837_684.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_120841_450.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_122046_665.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_122050_215.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_123954_049.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_123957_677.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_124339_743.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_124342_974.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_124805_308.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_124808_592.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_125453_025.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_125456_293.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_131009_675.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_131013_245.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_141631_595.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_141635_119.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_142848_009.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_142851_619.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_143232_968.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_143236_460.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_143529_448.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_143532_887.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_144214_561.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_144217_766.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_153737_135.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_153740_852.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_155558_324.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_155602_041.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_161105_235.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_161108_956.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_171916_161.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_171919_572.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_172624_346.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_172627_648.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_174531_102.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_174534_734.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_27072026_181446_168.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_27072026_181449_731.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_28072026_103417_155.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_28072026_103420_709.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_28072026_115141_022.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_28072026_115144_379.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_28072026_120909_793.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_28072026_120930_797.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_28072026_122251_427.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_28072026_122254_655.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_28072026_124520_256.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_28072026_124523_675.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_28072026_141112_404.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_28072026_141116_124.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_28072026_153856_847.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_28072026_153914_537.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_28072026_161833_106.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_28072026_161837_137.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_30072026_120444_612.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_30072026_120448_330.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_30072026_122522_969.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_30072026_122526_681.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_05082026_114323_772.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_05082026_114326_612.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_05082026_121505_990.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_05082026_121508_706.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_05082026_122350_894.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_05082026_122353_863.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_05082026_123030_390.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_05082026_123033_659.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_05082026_124421_069.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_05082026_124424_278.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_11082026_110843_888.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_11082026_110849_776.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_11082026_120344_955.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_11082026_120350_260.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_11082026_121024_018.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_11082026_121029_928.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_11082026_123007_148.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_11082026_123012_361.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_11082026_123419_099.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_11082026_123424_020.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_11082026_123931_656.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_11082026_123936_973.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_11082026_130750_454.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_11082026_130755_604.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_11082026_164502_504.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_11082026_164507_728.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Innovatiview\git\OPHC-New\.\src\test\resources\Reports\Medical Report_12082026_095653_384.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_12082026_095658_579.png</t>
+    <t>9999999998'</t>
+  </si>
+  <si>
+    <t>9999999988'</t>
+  </si>
+  <si>
+    <t>9999999888'</t>
+  </si>
+  <si>
+    <t>9999998888'</t>
+  </si>
+  <si>
+    <t>9999988888'</t>
+  </si>
+  <si>
+    <t>9999888888'</t>
+  </si>
+  <si>
+    <t>9998888888'</t>
+  </si>
+  <si>
+    <t>9988888888'</t>
+  </si>
+  <si>
+    <t>9888888888'</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_143949_557.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_12082026_143956_509.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_155103_900.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_12082026_155110_443.png</t>
   </si>
 </sst>
 </file>
@@ -834,13 +567,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="47.5546875" collapsed="true"/>
-    <col min="2" max="3" customWidth="true" width="82.6640625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="49.44140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="21.33203125" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" width="47.5546875"/>
+    <col min="2" max="3" customWidth="true" width="82.6640625"/>
+    <col min="4" max="4" customWidth="true" width="49.44140625"/>
+    <col min="5" max="5" customWidth="true" width="21.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="46.2">
@@ -853,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>137</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="23.4">
@@ -896,7 +629,7 @@
         <v>34</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>138</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -982,6 +715,51 @@
       </c>
       <c r="B25" s="8" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="B28" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="B29" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="B30" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="B31" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="B32" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s" s="0">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +773,7 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="34.33203125" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" width="34.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="33.6">

--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>OPHC</t>
   </si>
@@ -182,6 +182,12 @@
   </si>
   <si>
     <t>C:\TestData\MedicalReport_12082026_155110_443.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_162004_073.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_12082026_162010_250.png</t>
   </si>
 </sst>
 </file>
@@ -586,7 +592,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="23.4">
@@ -629,7 +635,7 @@
         <v>34</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:4">

--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>OPHC</t>
   </si>
@@ -188,6 +188,30 @@
   </si>
   <si>
     <t>C:\TestData\MedicalReport_12082026_162010_250.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_172926_616.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_12082026_172932_243.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_174424_027.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_12082026_174429_675.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_181114_990.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_12082026_181120_566.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_181545_666.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_12082026_181550_884.png</t>
   </si>
 </sst>
 </file>
@@ -592,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="23.4">
@@ -635,7 +659,7 @@
         <v>34</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">

--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>OPHC</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>C:\TestData\MedicalReport_12082026_181550_884.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_13082026_095333_273.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_13082026_095340_294.png</t>
   </si>
 </sst>
 </file>
@@ -616,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="23.4">
@@ -659,7 +665,7 @@
         <v>34</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4">

--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/803ce9435f8f2a27/Desktop/OPHC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{0821558B-90FF-490C-86E1-A2C1D1CA221C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1C6251-9732-4501-B5A7-23628257BC17}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{0821558B-90FF-490C-86E1-A2C1D1CA221C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05B1063A-FB59-4829-98D3-F9857F8BA384}"/>
   <bookViews>
     <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>OPHC</t>
   </si>
@@ -121,27 +121,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>C:\Users\VIKRAM\Desktop\OPHC\Images\2.jpeg</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\Desktop\OPHC\Images\Aadhaar_Card.jpeg</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\Desktop\OPHC\Images\Clinic_Hospital_Affiliation_Proof.jpeg</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\Desktop\OPHC\Images\Experience_Certificate.jpeg</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\Desktop\OPHC\Images\Medical_Degree_Certificate.jpeg</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\Desktop\OPHC\Images\NMC_State_Medical_Council_Certificate.jpeg</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\Desktop\OPHC\Images\PAN_Card.jpeg</t>
-  </si>
-  <si>
     <t>Doctor is a dedicated General Physician with over 12 years of clinical experience in diagnosing and treating a wide range of acute and chronic medical conditions. He specializes in diabetes management, hypertension, preventive healthcare, and infectious diseases. Dr.Kumar is committed to providing patient-centered care through accurate diagnosis, evidence-based treatment, and personalized health guidance.</t>
   </si>
   <si>
@@ -172,52 +151,49 @@
     <t>9888888888'</t>
   </si>
   <si>
-    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_143949_557.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_12082026_143956_509.png</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_155103_900.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_12082026_155110_443.png</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_162004_073.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_12082026_162010_250.png</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_172926_616.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_12082026_172932_243.png</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_174424_027.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_12082026_174429_675.png</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_181114_990.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_12082026_181120_566.png</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_12082026_181545_666.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_12082026_181550_884.png</t>
-  </si>
-  <si>
-    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_13082026_095333_273.png</t>
-  </si>
-  <si>
-    <t>C:\TestData\MedicalReport_13082026_095340_294.png</t>
+    <t>C:\Users\VIKRAM\Pictures\Doctors\Doctor.jpeg</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\Pictures\Doctors\Medical_Degree_Certificate.jpeg</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\Pictures\Doctors\NMC_State_Medical_Council_Certificate.jpeg</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\Pictures\Doctors\Aadhaar_Card.jpeg</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\Pictures\Doctors\PAN_Card.jpeg</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\Pictures\Doctors\Experience_Certificate.jpeg</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\Pictures\Doctors\Clinic_Hospital_Affiliation_Proof.jpeg</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_18082026_143816_968.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_18082026_143823_534.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_18082026_144242_698.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_18082026_144248_964.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_18082026_150257_093.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_18082026_150303_644.png</t>
+  </si>
+  <si>
+    <t>C:\Users\VIKRAM\git\OPHC_New\.\src\test\resources\Reports\Medical Report_18082026_152546_688.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_18082026_152553_483.png</t>
   </si>
 </sst>
 </file>
@@ -343,6 +319,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -622,7 +602,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="23.4">
@@ -646,7 +626,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -654,7 +634,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -662,10 +642,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -673,7 +653,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -681,7 +661,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -689,7 +669,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -697,7 +677,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -750,52 +730,52 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" t="s" s="0">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" t="s" s="0">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="B30" t="s" s="0">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" t="s" s="0">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="B32" t="s" s="0">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s" s="0">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s" s="0">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s" s="0">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s" s="0">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>OPHC</t>
   </si>
@@ -194,6 +194,15 @@
   </si>
   <si>
     <t>C:\TestData\MedicalReport_18082026_152553_483.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_19082026_144554_979.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_19082026_150237_648.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_19082026_161713_870.png</t>
   </si>
 </sst>
 </file>
@@ -645,7 +654,7 @@
         <v>41</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:4">

--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>OPHC</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>C:\TestData\MedicalReport_19082026_161713_870.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_19082026_163810_975.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_19082026_175921_461.png</t>
   </si>
 </sst>
 </file>
@@ -654,7 +660,7 @@
         <v>41</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4">

--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>OPHC</t>
   </si>
@@ -209,6 +209,12 @@
   </si>
   <si>
     <t>C:\TestData\MedicalReport_19082026_175921_461.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_20082026_102035_384.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_20082026_103510_595.png</t>
   </si>
 </sst>
 </file>
@@ -660,7 +666,7 @@
         <v>41</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">

--- a/src/test/resources/OPHC Automation Excel.xlsx
+++ b/src/test/resources/OPHC Automation Excel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>OPHC</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>C:\TestData\MedicalReport_20082026_103510_595.png</t>
+  </si>
+  <si>
+    <t>C:\TestData\MedicalReport_20082026_145446_014.png</t>
   </si>
 </sst>
 </file>
@@ -666,7 +669,7 @@
         <v>41</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4">
